--- a/data/raw/sales/Week 21/Nexlev/other_channels.xlsx
+++ b/data/raw/sales/Week 21/Nexlev/other_channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 21\Nexlev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAFCD74-65C0-4E43-A595-ED2F75E5EE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558C44AD-5186-47FA-95A9-BF426D37277E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2468,7 +2468,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:V59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -2477,10 +2477,10 @@
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="19.88671875" customWidth="1"/>
     <col min="6" max="6" width="11.6640625" customWidth="1"/>
-    <col min="7" max="22" width="8.6640625" customWidth="1"/>
+    <col min="7" max="21" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
@@ -2514,9 +2514,8 @@
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-    </row>
-    <row r="2" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>10</v>
       </c>
@@ -2533,10 +2532,10 @@
         <v>12</v>
       </c>
       <c r="F2" s="18">
-        <v>11028</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9346</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>10</v>
       </c>
@@ -2553,10 +2552,10 @@
         <v>23</v>
       </c>
       <c r="F3" s="18">
-        <v>44347</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>37582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>10</v>
       </c>
@@ -2573,10 +2572,10 @@
         <v>15</v>
       </c>
       <c r="F4" s="18">
-        <v>43485</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>36852</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>10</v>
       </c>
@@ -2593,10 +2592,10 @@
         <v>1</v>
       </c>
       <c r="F5" s="18">
-        <v>4199</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3558</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>10</v>
       </c>
@@ -2613,10 +2612,10 @@
         <v>2</v>
       </c>
       <c r="F6" s="18">
-        <v>2598</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>10</v>
       </c>
@@ -2633,10 +2632,10 @@
         <v>1</v>
       </c>
       <c r="F7" s="18">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>10</v>
       </c>
@@ -2653,10 +2652,10 @@
         <v>7</v>
       </c>
       <c r="F8" s="18">
-        <v>11543</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9782</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>10</v>
       </c>
@@ -2673,10 +2672,10 @@
         <v>7</v>
       </c>
       <c r="F9" s="18">
-        <v>12443</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10545</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>10</v>
       </c>
@@ -2696,7 +2695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>10</v>
       </c>
@@ -2713,10 +2712,10 @@
         <v>1</v>
       </c>
       <c r="F11" s="18">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>10</v>
       </c>
@@ -2736,7 +2735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
         <v>10</v>
       </c>
@@ -2753,10 +2752,10 @@
         <v>2</v>
       </c>
       <c r="F13" s="18">
-        <v>2998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>10</v>
       </c>
@@ -2773,10 +2772,10 @@
         <v>6</v>
       </c>
       <c r="F14" s="18">
-        <v>13494</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11436</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>10</v>
       </c>
@@ -2793,10 +2792,10 @@
         <v>3</v>
       </c>
       <c r="F15" s="18">
-        <v>10947</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>9277</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>10</v>
       </c>
@@ -2833,7 +2832,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="18">
-        <v>8997</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2873,7 +2872,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="18">
-        <v>4495</v>
+        <v>3809</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2973,7 +2972,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="18">
-        <v>10796</v>
+        <v>9149</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3013,7 +3012,7 @@
         <v>5</v>
       </c>
       <c r="F26" s="18">
-        <v>10495</v>
+        <v>8894</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3073,7 +3072,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="18">
-        <v>4598</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3113,7 +3112,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="18">
-        <v>1999</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3173,7 +3172,7 @@
         <v>9</v>
       </c>
       <c r="F34" s="18">
-        <v>14382</v>
+        <v>12188</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3213,7 +3212,7 @@
         <v>7</v>
       </c>
       <c r="F36" s="18">
-        <v>15193</v>
+        <v>12875</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3233,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="18">
-        <v>1699</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3253,7 +3252,7 @@
         <v>22</v>
       </c>
       <c r="F38" s="18">
-        <v>63778</v>
+        <v>54049</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3413,7 +3412,7 @@
         <v>2</v>
       </c>
       <c r="F46" s="18">
-        <v>1798</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3433,7 +3432,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="18">
-        <v>2098</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3633,7 +3632,7 @@
         <v>7</v>
       </c>
       <c r="F57" s="18">
-        <v>3493</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
